--- a/feedback_surveys/026_institutional_sustainability_goals_awareness_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/026_institutional_sustainability_goals_awareness_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>environmental_sustainability</t>
+          <t>environmental sustainability</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>operational_sustainability</t>
+          <t>operational sustainability</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>institutional_sustainability</t>
+          <t>institutional sustainability</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>campus_events</t>
+          <t>campus events</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>department_meetings</t>
+          <t>department meetings</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>faculty_meetings</t>
+          <t>faculty meetings</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>volunteer_opportunities</t>
+          <t>volunteer opportunities</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>course_content</t>
+          <t>course content</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>campus_activities</t>
+          <t>campus activities</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>department_meetings</t>
+          <t>department meetings</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>faculty_meetings</t>
+          <t>faculty meetings</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>text message</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>campus_portal</t>
+          <t>campus portal</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>department_meetings</t>
+          <t>department meetings</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>text message</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>campus_portal</t>
+          <t>campus portal</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>department_meetings</t>
+          <t>department meetings</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>faculty_meetings</t>
+          <t>faculty meetings</t>
         </is>
       </c>
     </row>
